--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B91ACE7-C3BE-4040-8B2D-5A1CF4526F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D7E0AB-4726-4189-A5B0-F8A7CF81796E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5616" yWindow="1368" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -5363,7 +5363,7 @@
         <v>1263</v>
       </c>
       <c r="T1" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="V1"/>
       <c r="W1"/>
@@ -5399,7 +5399,7 @@
         <v>1264</v>
       </c>
       <c r="T2" s="2">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
@@ -5436,7 +5436,7 @@
         <v>1265</v>
       </c>
       <c r="T3" s="2">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D7E0AB-4726-4189-A5B0-F8A7CF81796E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A829227-09F1-4DE5-A038-E745EB57F852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33390" yWindow="2115" windowWidth="28770" windowHeight="15450" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="BG" sheetId="2" r:id="rId2"/>
     <sheet name="PH" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$B$1:$D$166</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -79,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="1391">
   <si>
     <t>food</t>
   </si>
@@ -4245,13 +4249,6 @@
     <t>대구강북초등학교</t>
   </si>
   <si>
-    <t>203동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대구 북구 침산로21길 24</t>
-  </si>
-  <si>
     <t>대구 북구 옥산로17길 50</t>
   </si>
   <si>
@@ -4261,17 +4258,10 @@
     <t>대구 북구 매전로4길 9</t>
   </si>
   <si>
-    <t>212동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대구 북구 매전로4길 31</t>
   </si>
   <si>
     <t>대구 북구 매전로 50-42</t>
-  </si>
-  <si>
-    <t>대구 북구 공항로 16</t>
   </si>
   <si>
     <t>202동</t>
@@ -4291,32 +4281,12 @@
     <t>대구 북구 칠성남로 101</t>
   </si>
   <si>
-    <t>대구 북구 공항로 84</t>
-  </si>
-  <si>
-    <t>대구 북구 경대로5길 25</t>
-  </si>
-  <si>
     <t>대구 동구 신성로 60</t>
   </si>
   <si>
     <t>대구 동구 아양로9길 35</t>
   </si>
   <si>
-    <t>대구 북구 침산남로19길 9</t>
-  </si>
-  <si>
-    <t>대구 북구 침산로 163</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대구 북구 침산남로 90</t>
-  </si>
-  <si>
-    <t>505동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대구 북구 학정동로 40</t>
   </si>
   <si>
@@ -4327,10 +4297,6 @@
   </si>
   <si>
     <t>대구 북구 구암서로 41</t>
-  </si>
-  <si>
-    <t>303동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>대구 북구 구암서로 70</t>
@@ -4634,20 +4600,611 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대구 북구 복현동 241-1</t>
-  </si>
-  <si>
-    <t>대구 북구 국우동 1080</t>
-  </si>
-  <si>
-    <t>대구 북구 학정동 980</t>
+    <t>대구칠성초등학교</t>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호암로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 40</t>
+    </r>
+  </si>
+  <si>
+    <t>104동</t>
+  </si>
+  <si>
+    <t>106동</t>
+  </si>
+  <si>
+    <t>108동</t>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호암로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 20</t>
+    </r>
+  </si>
+  <si>
+    <t>105동</t>
+  </si>
+  <si>
+    <t>107동</t>
+  </si>
+  <si>
+    <t>110동</t>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칠성남로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 101</t>
+    </r>
+  </si>
+  <si>
+    <t>대구 북구 침산로 163</t>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>침산로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 163</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옥산로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 50</t>
+    </r>
+  </si>
+  <si>
+    <t>102동</t>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>침산남로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 90</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공항로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>북구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공항로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 84</t>
+    </r>
+  </si>
+  <si>
+    <t>103동</t>
+  </si>
+  <si>
+    <t>대구 북구 동북로 241</t>
+  </si>
+  <si>
+    <t>201동</t>
+  </si>
+  <si>
+    <t>202동</t>
+  </si>
+  <si>
+    <t>203동</t>
+  </si>
+  <si>
+    <t>101동</t>
+  </si>
+  <si>
+    <t>212동</t>
+  </si>
+  <si>
+    <t>대구사수초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 내곡로 49</t>
+  </si>
+  <si>
+    <t>대구 북구 내곡로 89</t>
+  </si>
+  <si>
+    <t>대구 북구 한강로 17</t>
+  </si>
+  <si>
+    <t>대구동평초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 동천로 97</t>
+  </si>
+  <si>
+    <t>대구 북구 대천로 101</t>
+  </si>
+  <si>
+    <t>대구 북구 동천로 156</t>
+  </si>
+  <si>
+    <t>109동</t>
+  </si>
+  <si>
+    <t>303동</t>
+  </si>
+  <si>
+    <t>305동</t>
+  </si>
+  <si>
+    <t>307동</t>
+  </si>
+  <si>
+    <t>205동</t>
+  </si>
+  <si>
+    <t>309동</t>
+  </si>
+  <si>
+    <t>대구연경초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 연경중앙로11길 19</t>
+  </si>
+  <si>
+    <t>대구 북구 동화천로 315</t>
+  </si>
+  <si>
+    <t>204동</t>
+  </si>
+  <si>
+    <t>대구 동구 동화천로 369</t>
+  </si>
+  <si>
+    <t>대구 동구 신암남로 50</t>
+  </si>
+  <si>
+    <t>대구동변초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 동변로 55</t>
+  </si>
+  <si>
+    <t>대구 북구 동변로 50</t>
+  </si>
+  <si>
+    <t>대구 북구 동변로20길 20</t>
+  </si>
+  <si>
+    <t>대구도남초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 도남로 144</t>
+  </si>
+  <si>
+    <t>대구 북구 도남로 154</t>
+  </si>
+  <si>
+    <t>대구 북구 도남로 114</t>
+  </si>
+  <si>
+    <t>대구 북구 학남로 100</t>
+  </si>
+  <si>
+    <t>대구삼영초등학교</t>
+  </si>
+  <si>
+    <t>대구운암초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 학정동로 7</t>
+  </si>
+  <si>
+    <t>대구칠곡초등학교</t>
+  </si>
+  <si>
+    <t>대구 북구 칠곡중앙대로110길 5</t>
+  </si>
+  <si>
+    <t>대구태암초등학교</t>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4739,6 +5296,13 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -4873,7 +5437,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4905,9 +5469,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4963,6 +5524,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5311,32 +5878,32 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:X501"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="48.59765625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="48.625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" style="2"/>
-    <col min="11" max="12" width="10.59765625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.69921875"/>
+    <col min="11" max="12" width="10.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.75"/>
     <col min="14" max="14" width="9" style="2"/>
-    <col min="15" max="16" width="10.59765625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.69921875"/>
+    <col min="15" max="16" width="10.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="8.75"/>
     <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="20.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
       <c r="F1" s="6" t="s">
         <v>56</v>
       </c>
@@ -5371,7 +5938,7 @@
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="2"/>
-      <c r="B2" s="14"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="2"/>
       <c r="F2" s="3" t="s">
         <v>59</v>
@@ -5408,7 +5975,7 @@
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="2"/>
-      <c r="B3" s="14"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="2"/>
       <c r="F3" s="3" t="s">
         <v>60</v>
@@ -5445,7 +6012,7 @@
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="2"/>
-      <c r="B4" s="14"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="2"/>
       <c r="F4" s="3" t="s">
         <v>61</v>
@@ -5472,7 +6039,7 @@
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="2"/>
-      <c r="B5" s="14"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="2"/>
       <c r="F5" s="3" t="s">
         <v>62</v>
@@ -5495,16 +6062,16 @@
       <c r="P5" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="R5" s="21" t="s">
-        <v>1305</v>
-      </c>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="23"/>
+      <c r="R5" s="20" t="s">
+        <v>1294</v>
+      </c>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="22"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="2"/>
-      <c r="B6" s="14"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="2"/>
       <c r="F6" s="3" t="s">
         <v>63</v>
@@ -5527,14 +6094,14 @@
       <c r="P6" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="R6" s="24"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="26"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="25"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="2"/>
-      <c r="B7" s="14"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="2"/>
       <c r="F7" s="3" t="s">
         <v>64</v>
@@ -5557,14 +6124,14 @@
       <c r="P7" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="R7" s="24"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="26"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="25"/>
     </row>
     <row r="8" spans="1:24" ht="16.5" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="14"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="2"/>
       <c r="F8" s="3" t="s">
         <v>65</v>
@@ -5587,14 +6154,14 @@
       <c r="P8" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="R8" s="24"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="26"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="25"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="2"/>
-      <c r="B9" s="14"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="2"/>
       <c r="F9" s="3" t="s">
         <v>66</v>
@@ -5617,14 +6184,14 @@
       <c r="P9" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="R9" s="24"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="26"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="25"/>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="2"/>
-      <c r="B10" s="14"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="2"/>
       <c r="F10" s="3" t="s">
         <v>67</v>
@@ -5647,14 +6214,14 @@
       <c r="P10" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="R10" s="24"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="26"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="25"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="2"/>
-      <c r="B11" s="14"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="2"/>
       <c r="F11" s="3" t="s">
         <v>68</v>
@@ -5677,14 +6244,14 @@
       <c r="P11" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="R11" s="24"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="26"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="25"/>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="2"/>
-      <c r="B12" s="14"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="2"/>
       <c r="F12" s="3" t="s">
         <v>69</v>
@@ -5707,14 +6274,14 @@
       <c r="P12" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="R12" s="24"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="26"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="25"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="2"/>
-      <c r="B13" s="14"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="2"/>
       <c r="F13" s="3" t="s">
         <v>70</v>
@@ -5737,14 +6304,14 @@
       <c r="P13" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="R13" s="24"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="26"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="2"/>
-      <c r="B14" s="14"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="2"/>
       <c r="F14" s="3" t="s">
         <v>71</v>
@@ -5767,14 +6334,14 @@
       <c r="P14" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="R14" s="24"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="26"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="25"/>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="2"/>
-      <c r="B15" s="15"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="2"/>
       <c r="F15" s="3" t="s">
         <v>72</v>
@@ -5797,14 +6364,14 @@
       <c r="P15" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="R15" s="24"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="26"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="25"/>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="2"/>
-      <c r="B16" s="14"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="2"/>
       <c r="F16" s="3" t="s">
         <v>73</v>
@@ -5827,14 +6394,14 @@
       <c r="P16" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="R16" s="24"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="26"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="25"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="2"/>
-      <c r="B17" s="14"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="2"/>
       <c r="F17" s="3" t="s">
         <v>74</v>
@@ -5857,14 +6424,14 @@
       <c r="P17" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="R17" s="24"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="26"/>
-    </row>
-    <row r="18" spans="1:21" ht="19.2">
+      <c r="R17" s="23"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="25"/>
+    </row>
+    <row r="18" spans="1:21" ht="17.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="16"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="2"/>
       <c r="F18" s="3" t="s">
         <v>75</v>
@@ -5887,14 +6454,14 @@
       <c r="P18" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="R18" s="27"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="29"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="28"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="2"/>
-      <c r="B19" s="14"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="2"/>
       <c r="F19" s="3" t="s">
         <v>76</v>
@@ -5920,7 +6487,7 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="2"/>
-      <c r="B20" s="15"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="2"/>
       <c r="F20" s="3" t="s">
         <v>0</v>
@@ -5946,7 +6513,7 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="2"/>
-      <c r="B21" s="14"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="2"/>
       <c r="F21" s="3" t="s">
         <v>77</v>
@@ -5970,9 +6537,9 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="19.2">
+    <row r="22" spans="1:21" ht="17.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="17"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="2"/>
       <c r="F22" s="3" t="s">
         <v>78</v>
@@ -5998,7 +6565,7 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="2"/>
-      <c r="B23" s="14"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="2"/>
       <c r="F23" s="3" t="s">
         <v>79</v>
@@ -6024,7 +6591,7 @@
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="2"/>
-      <c r="B24" s="14"/>
+      <c r="B24" s="13"/>
       <c r="C24" s="2"/>
       <c r="F24" s="3" t="s">
         <v>80</v>
@@ -6050,7 +6617,7 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="2"/>
-      <c r="B25" s="14"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="2"/>
       <c r="F25" s="3" t="s">
         <v>81</v>
@@ -6076,7 +6643,7 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="2"/>
-      <c r="B26" s="14"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="2"/>
       <c r="F26" s="3" t="s">
         <v>82</v>
@@ -6102,7 +6669,7 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="2"/>
-      <c r="B27" s="14"/>
+      <c r="B27" s="13"/>
       <c r="C27" s="2"/>
       <c r="F27" s="3" t="s">
         <v>83</v>
@@ -6128,7 +6695,7 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="2"/>
-      <c r="B28" s="14"/>
+      <c r="B28" s="13"/>
       <c r="C28" s="2"/>
       <c r="F28" s="3" t="s">
         <v>84</v>
@@ -6153,9 +6720,9 @@
       </c>
     </row>
     <row r="29" spans="1:21">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="18"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="17"/>
       <c r="F29" s="3" t="s">
         <v>85</v>
       </c>
@@ -6179,9 +6746,9 @@
       </c>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="17"/>
       <c r="F30" s="3" t="s">
         <v>86</v>
       </c>
@@ -6205,9 +6772,9 @@
       </c>
     </row>
     <row r="31" spans="1:21">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="17"/>
       <c r="F31" s="3" t="s">
         <v>87</v>
       </c>
@@ -6231,9 +6798,9 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="18"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="17"/>
       <c r="F32" s="3" t="s">
         <v>88</v>
       </c>
@@ -6257,9 +6824,9 @@
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="18"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="17"/>
       <c r="F33" s="3" t="s">
         <v>89</v>
       </c>
@@ -6283,9 +6850,9 @@
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="18"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="17"/>
       <c r="F34" s="3" t="s">
         <v>90</v>
       </c>
@@ -6309,9 +6876,9 @@
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="18"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="17"/>
       <c r="F35" s="3" t="s">
         <v>91</v>
       </c>
@@ -6335,9 +6902,9 @@
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="18"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="17"/>
       <c r="F36" s="3" t="s">
         <v>92</v>
       </c>
@@ -6361,9 +6928,9 @@
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="18"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="17"/>
       <c r="F37" s="3" t="s">
         <v>93</v>
       </c>
@@ -6387,9 +6954,9 @@
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="18"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="18"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="17"/>
       <c r="F38" s="3" t="s">
         <v>94</v>
       </c>
@@ -6413,9 +6980,9 @@
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="18"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="17"/>
       <c r="F39" s="3" t="s">
         <v>95</v>
       </c>
@@ -6439,9 +7006,9 @@
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="18"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="18"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="17"/>
       <c r="F40" s="3" t="s">
         <v>96</v>
       </c>
@@ -6465,9 +7032,9 @@
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="18"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="17"/>
       <c r="F41" s="3" t="s">
         <v>97</v>
       </c>
@@ -6491,9 +7058,9 @@
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="18"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="18"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="17"/>
       <c r="F42" s="3" t="s">
         <v>98</v>
       </c>
@@ -6517,9 +7084,9 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="18"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="18"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="17"/>
       <c r="F43" s="3" t="s">
         <v>99</v>
       </c>
@@ -6543,9 +7110,9 @@
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="18"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="18"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="17"/>
       <c r="F44" s="3" t="s">
         <v>100</v>
       </c>
@@ -6569,9 +7136,9 @@
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="18"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="18"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="17"/>
       <c r="F45" s="3" t="s">
         <v>101</v>
       </c>
@@ -6595,9 +7162,9 @@
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="18"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="17"/>
       <c r="F46" s="3" t="s">
         <v>102</v>
       </c>
@@ -10968,17 +11535,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1EB988-2ED1-436F-8BF0-F3686DC619B0}">
-  <dimension ref="A1:T28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <dimension ref="A1:T166"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
     <col min="5" max="16" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -10987,7 +11554,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1304</v>
+        <v>1293</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>10</v>
@@ -10996,42 +11563,42 @@
       <c r="G1"/>
       <c r="H1"/>
       <c r="S1" s="2" t="s">
-        <v>1335</v>
+        <v>1324</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>1332</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1276</v>
+        <v>1329</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>1330</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>1331</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="S2" s="2" t="s">
-        <v>1336</v>
+        <v>1325</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>1333</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>1277</v>
+        <v>1329</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>1330</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>1332</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
@@ -11040,279 +11607,1375 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>1278</v>
+        <v>1329</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>1330</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>1279</v>
+        <v>1329</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>1334</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1280</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>1281</v>
+        <v>1329</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>1334</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1275</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>1282</v>
+        <v>1329</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>1334</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1284</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>1283</v>
+        <v>1329</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>1338</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>42</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>1340</v>
+        <v>1329</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>1338</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>1289</v>
+        <v>1329</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>1338</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>1285</v>
+        <v>1268</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>1344</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>1286</v>
+        <v>1268</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>1344</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1287</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>1288</v>
+        <v>1268</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>1344</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>1290</v>
+        <v>1268</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>1345</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>1291</v>
+        <v>1268</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>1345</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>1292</v>
+        <v>1268</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>1345</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>1293</v>
+        <v>1268</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1347</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="19.2">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>1294</v>
+        <v>1268</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1347</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>1295</v>
+        <v>1268</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1347</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>1341</v>
+        <v>1267</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1277</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1296</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>1297</v>
+        <v>1267</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1278</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1275</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>1342</v>
+        <v>1267</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1279</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>1298</v>
+        <v>1353</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1354</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>1297</v>
+        <v>1353</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1354</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1284</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>1299</v>
+        <v>1353</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1354</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>1300</v>
+        <v>1353</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1355</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1301</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>1302</v>
+        <v>1353</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1355</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1275</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>1303</v>
+        <v>1353</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1355</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1262</v>
-      </c>
-    </row>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+    </row>
+    <row r="129" s="2" customFormat="1"/>
+    <row r="130" s="2" customFormat="1"/>
+    <row r="131" s="2" customFormat="1"/>
+    <row r="132" s="2" customFormat="1"/>
+    <row r="133" s="2" customFormat="1"/>
+    <row r="134" s="2" customFormat="1"/>
+    <row r="135" s="2" customFormat="1"/>
+    <row r="136" s="2" customFormat="1"/>
+    <row r="137" s="2" customFormat="1"/>
+    <row r="138" s="2" customFormat="1"/>
+    <row r="139" s="2" customFormat="1"/>
+    <row r="140" s="2" customFormat="1"/>
+    <row r="141" s="2" customFormat="1"/>
+    <row r="142" s="2" customFormat="1"/>
+    <row r="143" s="2" customFormat="1"/>
+    <row r="144" s="2" customFormat="1"/>
+    <row r="145" s="2" customFormat="1"/>
+    <row r="146" s="2" customFormat="1"/>
+    <row r="147" s="2" customFormat="1"/>
+    <row r="148" s="2" customFormat="1"/>
+    <row r="149" s="2" customFormat="1"/>
+    <row r="150" s="2" customFormat="1"/>
+    <row r="151" s="2" customFormat="1"/>
+    <row r="152" s="2" customFormat="1"/>
+    <row r="153" s="2" customFormat="1"/>
+    <row r="154" s="2" customFormat="1"/>
+    <row r="155" s="2" customFormat="1"/>
+    <row r="156" s="2" customFormat="1"/>
+    <row r="157" s="2" customFormat="1"/>
+    <row r="158" s="2" customFormat="1"/>
+    <row r="159" s="2" customFormat="1"/>
+    <row r="160" s="2" customFormat="1"/>
+    <row r="161" s="2" customFormat="1"/>
+    <row r="162" s="2" customFormat="1"/>
+    <row r="163" s="2" customFormat="1"/>
+    <row r="164" s="2" customFormat="1"/>
+    <row r="165" s="2" customFormat="1"/>
+    <row r="166" s="2" customFormat="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -11320,20 +12983,21 @@
     <hyperlink ref="T1" r:id="rId2" xr:uid="{8F219EA8-D524-4446-92E1-32AFF88D35DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801651D1-1060-4046-8C27-A9334BE84870}">
   <dimension ref="A1:T63"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="5" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.3984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -11341,7 +13005,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1304</v>
+        <v>1293</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>10</v>
@@ -11402,7 +13066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.2">
+    <row r="7" spans="1:3" ht="17.25">
       <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
@@ -11446,7 +13110,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="19.2">
+    <row r="11" spans="1:3" ht="17.25">
       <c r="A11" s="7" t="s">
         <v>5</v>
       </c>
@@ -11468,7 +13132,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="19.2">
+    <row r="13" spans="1:3" ht="17.25">
       <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
@@ -11534,10 +13198,10 @@
         <v>38</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>1334</v>
+        <v>1323</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>1338</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -11551,10 +13215,10 @@
         <v>39</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>1337</v>
+        <v>1326</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>1339</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -11658,10 +13322,10 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="7" t="s">
-        <v>1306</v>
+        <v>1295</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>12</v>
@@ -11669,21 +13333,21 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="7" t="s">
-        <v>1306</v>
+        <v>1295</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1313</v>
+        <v>1302</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="7" t="s">
-        <v>1306</v>
+        <v>1295</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>12</v>
@@ -11691,10 +13355,10 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32" s="7" t="s">
-        <v>1307</v>
+        <v>1296</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1315</v>
+        <v>1304</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>42</v>
@@ -11702,7 +13366,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>1307</v>
+        <v>1296</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>17</v>
@@ -11713,10 +13377,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
-        <v>1307</v>
+        <v>1296</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1319</v>
+        <v>1308</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>13</v>
@@ -11724,10 +13388,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
-        <v>1308</v>
+        <v>1297</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1316</v>
+        <v>1305</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>12</v>
@@ -11735,43 +13399,43 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>1308</v>
+        <v>1297</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1317</v>
+        <v>1306</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1318</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="7" t="s">
-        <v>1308</v>
+        <v>1297</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>1320</v>
+        <v>1309</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="19.2">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="17.25">
       <c r="A38" s="7" t="s">
-        <v>1309</v>
+        <v>1298</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1322</v>
+        <v>1311</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="7" t="s">
-        <v>1309</v>
+        <v>1298</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1323</v>
+        <v>1312</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>16</v>
@@ -11779,10 +13443,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="7" t="s">
-        <v>1309</v>
+        <v>1298</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1324</v>
+        <v>1313</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>12</v>
@@ -11790,32 +13454,32 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>1310</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="19.2">
+    </row>
+    <row r="42" spans="1:3" ht="17.25">
       <c r="A42" s="7" t="s">
-        <v>1310</v>
+        <v>1299</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1326</v>
+        <v>1315</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1327</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="7" t="s">
-        <v>1310</v>
+        <v>1299</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1328</v>
+        <v>1317</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>12</v>
@@ -11823,10 +13487,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="7" t="s">
-        <v>1311</v>
+        <v>1300</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1329</v>
+        <v>1318</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>13</v>
@@ -11834,10 +13498,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="7" t="s">
-        <v>1311</v>
+        <v>1300</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>42</v>
@@ -11845,10 +13509,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="7" t="s">
-        <v>1311</v>
+        <v>1300</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1331</v>
+        <v>1320</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>39</v>
@@ -11947,4 +13611,2016 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECF04CD-0782-4755-8611-A09CA217F0DE}">
+  <dimension ref="A1:D166"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="30" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="30"/>
+      <c r="B3" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="30"/>
+      <c r="B4" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="30"/>
+      <c r="B5" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="30"/>
+      <c r="B6" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="30"/>
+      <c r="B7" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="30"/>
+      <c r="B8" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="30"/>
+      <c r="B9" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="30"/>
+      <c r="B10" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="30"/>
+      <c r="B11" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="30"/>
+      <c r="B12" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="30"/>
+      <c r="B13" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="30"/>
+      <c r="B14" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="30"/>
+      <c r="B15" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="30"/>
+      <c r="B16" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="30"/>
+      <c r="B17" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="30"/>
+      <c r="B18" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="30"/>
+      <c r="B19" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="30"/>
+      <c r="B20" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="30"/>
+      <c r="B21" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="30"/>
+      <c r="B22" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="30"/>
+      <c r="B23" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="30"/>
+      <c r="B24" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="30"/>
+      <c r="B25" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="30"/>
+      <c r="B26" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="30"/>
+      <c r="B27" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="30"/>
+      <c r="B28" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="30"/>
+      <c r="B29" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="30"/>
+      <c r="B30" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="30"/>
+      <c r="B31" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="30"/>
+      <c r="B32" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="30"/>
+      <c r="B33" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="30"/>
+      <c r="B34" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="30"/>
+      <c r="B35" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="30"/>
+      <c r="B36" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="30"/>
+      <c r="B37" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="30"/>
+      <c r="B38" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="30"/>
+      <c r="B39" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="30"/>
+      <c r="B40" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="30"/>
+      <c r="B41" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="30"/>
+      <c r="B42" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="30"/>
+      <c r="B43" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="30"/>
+      <c r="B44" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="30"/>
+      <c r="B45" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="30"/>
+      <c r="B46" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="30"/>
+      <c r="B47" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="30"/>
+      <c r="B48" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="30"/>
+      <c r="B49" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="30"/>
+      <c r="B50" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="30"/>
+      <c r="B51" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="30"/>
+      <c r="B52" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C52" s="29" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="30"/>
+      <c r="B53" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="30"/>
+      <c r="B54" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C54" s="29" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="30"/>
+      <c r="B55" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="30"/>
+      <c r="B56" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="30"/>
+      <c r="B57" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="30"/>
+      <c r="B58" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="30"/>
+      <c r="B59" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="30"/>
+      <c r="B60" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="30"/>
+      <c r="B61" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="30"/>
+      <c r="B62" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="30"/>
+      <c r="B63" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="30"/>
+      <c r="B64" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="30"/>
+      <c r="B65" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="30"/>
+      <c r="B66" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="30"/>
+      <c r="B67" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="30"/>
+      <c r="B68" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="30"/>
+      <c r="B69" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="30"/>
+      <c r="B70" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="30"/>
+      <c r="B71" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="30"/>
+      <c r="B72" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="30"/>
+      <c r="B73" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="30"/>
+      <c r="B74" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="30"/>
+      <c r="B75" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="30"/>
+      <c r="B76" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="30"/>
+      <c r="B77" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="30"/>
+      <c r="B78" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="30"/>
+      <c r="B79" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="30"/>
+      <c r="B80" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="30"/>
+      <c r="B81" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="30"/>
+      <c r="B82" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="30"/>
+      <c r="B83" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="30"/>
+      <c r="B84" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="30"/>
+      <c r="B85" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="30"/>
+      <c r="B86" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="30"/>
+      <c r="B87" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="30"/>
+      <c r="B88" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="30"/>
+      <c r="B89" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="30"/>
+      <c r="B90" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="30"/>
+      <c r="B91" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="30"/>
+      <c r="B92" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="30"/>
+      <c r="B93" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="30"/>
+      <c r="B94" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="30"/>
+      <c r="B95" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="30"/>
+      <c r="B96" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="30"/>
+      <c r="B97" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="30"/>
+      <c r="B98" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="30"/>
+      <c r="B99" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="30"/>
+      <c r="B100" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="30"/>
+      <c r="B101" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="30"/>
+      <c r="B102" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="30"/>
+      <c r="B103" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="30"/>
+      <c r="B104" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="30"/>
+      <c r="B105" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="30"/>
+      <c r="B106" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="30"/>
+      <c r="B107" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="30"/>
+      <c r="B108" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="30"/>
+      <c r="B109" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="30"/>
+      <c r="B110" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="30"/>
+      <c r="B111" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="30"/>
+      <c r="B112" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="30"/>
+      <c r="B113" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="30"/>
+      <c r="B114" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="30"/>
+      <c r="B115" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="30"/>
+      <c r="B116" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="30"/>
+      <c r="B117" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="30"/>
+      <c r="B118" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="30"/>
+      <c r="B119" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="30"/>
+      <c r="B120" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="30"/>
+      <c r="B121" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="30"/>
+      <c r="B122" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C122" s="29" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="30"/>
+      <c r="B123" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C123" s="29" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="30"/>
+      <c r="B124" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C124" s="29" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="30"/>
+      <c r="B125" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C125" s="29" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="30"/>
+      <c r="B126" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C126" s="29" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="30"/>
+      <c r="B127" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C127" s="29" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="30"/>
+      <c r="B128" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C128" s="29" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="30"/>
+      <c r="B129" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C129" s="29" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="30"/>
+      <c r="B130" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C130" s="29" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="30"/>
+      <c r="B131" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C131" s="29" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="30"/>
+      <c r="B132" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C132" s="29" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="30"/>
+      <c r="B133" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C133" s="29" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="30"/>
+      <c r="B134" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C134" s="29" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="30"/>
+      <c r="B135" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C135" s="29" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="17.25">
+      <c r="A136" s="30"/>
+      <c r="B136" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="30"/>
+      <c r="B137" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C137" s="29" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="30"/>
+      <c r="B138" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C138" s="29" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="30"/>
+      <c r="B139" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C139" s="29" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="30"/>
+      <c r="B140" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="30"/>
+      <c r="B141" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="30"/>
+      <c r="B142" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="30"/>
+      <c r="B143" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="30"/>
+      <c r="B144" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="30"/>
+      <c r="B145" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="30"/>
+      <c r="B146" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="30"/>
+      <c r="B147" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="30"/>
+      <c r="B148" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="30"/>
+      <c r="B149" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="30"/>
+      <c r="B150" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="30"/>
+      <c r="B151" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="30"/>
+      <c r="B152" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="30"/>
+      <c r="B153" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="30"/>
+      <c r="B154" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="30"/>
+      <c r="B155" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="30"/>
+      <c r="B156" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="30"/>
+      <c r="B157" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="30"/>
+      <c r="B158" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="30"/>
+      <c r="B159" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="30"/>
+      <c r="B160" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="30"/>
+      <c r="B161" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="30"/>
+      <c r="B162" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="30"/>
+      <c r="B163" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="30"/>
+      <c r="B164" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="30"/>
+      <c r="B165" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="30"/>
+      <c r="B166" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:D166" xr:uid="{9ECF04CD-0782-4755-8611-A09CA217F0DE}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A166"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A829227-09F1-4DE5-A038-E745EB57F852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1854BF3-26A9-4B08-B73E-9BFDC3979107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33390" yWindow="2115" windowWidth="28770" windowHeight="15450" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50730" yWindow="2085" windowWidth="28770" windowHeight="15450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -5498,6 +5498,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5524,9 +5527,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6062,12 +6062,12 @@
       <c r="P5" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="R5" s="20" t="s">
+      <c r="R5" s="21" t="s">
         <v>1294</v>
       </c>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="23"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="2"/>
@@ -6094,10 +6094,10 @@
       <c r="P6" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="R6" s="23"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="25"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="26"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="2"/>
@@ -6124,10 +6124,10 @@
       <c r="P7" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="R7" s="23"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="25"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="26"/>
     </row>
     <row r="8" spans="1:24" ht="16.5" customHeight="1">
       <c r="A8" s="2"/>
@@ -6154,10 +6154,10 @@
       <c r="P8" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="R8" s="23"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="25"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="26"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="2"/>
@@ -6184,10 +6184,10 @@
       <c r="P9" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="R9" s="23"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="25"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="26"/>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="2"/>
@@ -6214,10 +6214,10 @@
       <c r="P10" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="R10" s="23"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="25"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="26"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="2"/>
@@ -6244,10 +6244,10 @@
       <c r="P11" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="R11" s="23"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="25"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="26"/>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="2"/>
@@ -6274,10 +6274,10 @@
       <c r="P12" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="R12" s="23"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="25"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="26"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="2"/>
@@ -6304,10 +6304,10 @@
       <c r="P13" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="R13" s="23"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="25"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="26"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="2"/>
@@ -6334,10 +6334,10 @@
       <c r="P14" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="R14" s="23"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="25"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="26"/>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="2"/>
@@ -6364,10 +6364,10 @@
       <c r="P15" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="R15" s="23"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="25"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="26"/>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="2"/>
@@ -6394,10 +6394,10 @@
       <c r="P16" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="R16" s="23"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="25"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="26"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="2"/>
@@ -6424,10 +6424,10 @@
       <c r="P17" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="R17" s="23"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="25"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="26"/>
     </row>
     <row r="18" spans="1:21" ht="17.25">
       <c r="A18" s="2"/>
@@ -6454,10 +6454,10 @@
       <c r="P18" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="R18" s="26"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="28"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="29"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="2"/>
@@ -11542,8 +11542,9 @@
     <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
-    <col min="5" max="16" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="17" max="18" width="9" style="2"/>
+    <col min="5" max="16" width="9" style="2" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="0" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="2"/>
     <col min="19" max="19" width="12.375" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
@@ -11573,7 +11574,7 @@
       <c r="A2" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="20" t="s">
         <v>1330</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11594,7 +11595,7 @@
       <c r="A3" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="20" t="s">
         <v>1330</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11609,7 +11610,7 @@
       <c r="A4" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="20" t="s">
         <v>1330</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -11620,7 +11621,7 @@
       <c r="A5" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="20" t="s">
         <v>1334</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -11631,7 +11632,7 @@
       <c r="A6" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="20" t="s">
         <v>1334</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -11642,7 +11643,7 @@
       <c r="A7" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="20" t="s">
         <v>1334</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -11653,7 +11654,7 @@
       <c r="A8" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="20" t="s">
         <v>1338</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -11664,7 +11665,7 @@
       <c r="A9" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="20" t="s">
         <v>1338</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -11675,7 +11676,7 @@
       <c r="A10" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="20" t="s">
         <v>1338</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -11686,7 +11687,7 @@
       <c r="A11" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="20" t="s">
         <v>1344</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -11697,7 +11698,7 @@
       <c r="A12" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="20" t="s">
         <v>1344</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -11708,7 +11709,7 @@
       <c r="A13" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="20" t="s">
         <v>1344</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -11719,7 +11720,7 @@
       <c r="A14" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="20" t="s">
         <v>1345</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -11730,7 +11731,7 @@
       <c r="A15" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="20" t="s">
         <v>1345</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -11741,7 +11742,7 @@
       <c r="A16" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="20" t="s">
         <v>1345</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -13000,7 +13001,7 @@
     <col min="20" max="20" width="48.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:20">
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
@@ -13010,8 +13011,14 @@
       <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="S1" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -13021,8 +13028,14 @@
       <c r="C2" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="S2" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
@@ -13033,7 +13046,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:20">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -13044,7 +13057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:20">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
@@ -13055,7 +13068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:20">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -13066,7 +13079,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25">
+    <row r="7" spans="1:20" ht="17.25">
       <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
@@ -13077,7 +13090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:20">
       <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
@@ -13088,7 +13101,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:20">
       <c r="A9" s="7" t="s">
         <v>4</v>
       </c>
@@ -13099,7 +13112,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:20">
       <c r="A10" s="7" t="s">
         <v>1260</v>
       </c>
@@ -13110,7 +13123,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25">
+    <row r="11" spans="1:20" ht="17.25">
       <c r="A11" s="7" t="s">
         <v>5</v>
       </c>
@@ -13121,7 +13134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:20">
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
@@ -13132,7 +13145,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.25">
+    <row r="13" spans="1:20" ht="17.25">
       <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
@@ -13143,7 +13156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:20">
       <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
@@ -13154,7 +13167,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:20">
       <c r="A15" s="7" t="s">
         <v>32</v>
       </c>
@@ -13165,7 +13178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:20">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -13176,7 +13189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -13187,7 +13200,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
         <v>6</v>
       </c>
@@ -13197,14 +13210,8 @@
       <c r="C18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="S18" s="2" t="s">
-        <v>1323</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
         <v>6</v>
       </c>
@@ -13214,14 +13221,8 @@
       <c r="C19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>1326</v>
-      </c>
-      <c r="T19" s="10" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
         <v>7</v>
       </c>
@@ -13232,7 +13233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
@@ -13243,7 +13244,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:3">
       <c r="A22" s="7" t="s">
         <v>7</v>
       </c>
@@ -13254,7 +13255,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:3">
       <c r="A23" s="7" t="s">
         <v>8</v>
       </c>
@@ -13265,7 +13266,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:3">
       <c r="A24" s="7" t="s">
         <v>8</v>
       </c>
@@ -13276,7 +13277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:3">
       <c r="A25" s="7" t="s">
         <v>8</v>
       </c>
@@ -13287,7 +13288,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:3">
       <c r="A26" s="7" t="s">
         <v>52</v>
       </c>
@@ -13298,7 +13299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:3">
       <c r="A27" s="7" t="s">
         <v>52</v>
       </c>
@@ -13309,7 +13310,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:3">
       <c r="A28" s="7" t="s">
         <v>52</v>
       </c>
@@ -13320,7 +13321,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:3">
       <c r="A29" s="7" t="s">
         <v>1295</v>
       </c>
@@ -13331,7 +13332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:3">
       <c r="A30" s="7" t="s">
         <v>1295</v>
       </c>
@@ -13342,7 +13343,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:3">
       <c r="A31" s="7" t="s">
         <v>1295</v>
       </c>
@@ -13353,7 +13354,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:3">
       <c r="A32" s="7" t="s">
         <v>1296</v>
       </c>
@@ -13606,8 +13607,8 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="T19" r:id="rId1" xr:uid="{D0C91E0B-1806-4CAB-BCA7-78D6EF84E892}"/>
-    <hyperlink ref="T18" r:id="rId2" xr:uid="{7086A333-C750-40EE-AA7A-B21852C6C844}"/>
+    <hyperlink ref="T2" r:id="rId1" xr:uid="{D0C91E0B-1806-4CAB-BCA7-78D6EF84E892}"/>
+    <hyperlink ref="T1" r:id="rId2" xr:uid="{7086A333-C750-40EE-AA7A-B21852C6C844}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14216,7 +14217,7 @@
       <c r="B50" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="20" t="s">
         <v>1344</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -14228,7 +14229,7 @@
       <c r="B51" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="20" t="s">
         <v>1344</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -14240,7 +14241,7 @@
       <c r="B52" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="20" t="s">
         <v>1344</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -14252,7 +14253,7 @@
       <c r="B53" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="20" t="s">
         <v>1345</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -14264,7 +14265,7 @@
       <c r="B54" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="20" t="s">
         <v>1345</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -14276,7 +14277,7 @@
       <c r="B55" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="20" t="s">
         <v>1345</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -15080,7 +15081,7 @@
       <c r="B122" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C122" s="20" t="s">
         <v>1330</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -15092,7 +15093,7 @@
       <c r="B123" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C123" s="29" t="s">
+      <c r="C123" s="20" t="s">
         <v>1330</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -15104,7 +15105,7 @@
       <c r="B124" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C124" s="20" t="s">
         <v>1330</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -15116,7 +15117,7 @@
       <c r="B125" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C125" s="29" t="s">
+      <c r="C125" s="20" t="s">
         <v>1334</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -15128,7 +15129,7 @@
       <c r="B126" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C126" s="29" t="s">
+      <c r="C126" s="20" t="s">
         <v>1334</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -15140,7 +15141,7 @@
       <c r="B127" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C127" s="29" t="s">
+      <c r="C127" s="20" t="s">
         <v>1334</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -15152,7 +15153,7 @@
       <c r="B128" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C128" s="29" t="s">
+      <c r="C128" s="20" t="s">
         <v>1338</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -15164,7 +15165,7 @@
       <c r="B129" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C129" s="29" t="s">
+      <c r="C129" s="20" t="s">
         <v>1338</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -15176,7 +15177,7 @@
       <c r="B130" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C130" s="29" t="s">
+      <c r="C130" s="20" t="s">
         <v>1338</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -15188,7 +15189,7 @@
       <c r="B131" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C131" s="29" t="s">
+      <c r="C131" s="20" t="s">
         <v>1340</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -15200,7 +15201,7 @@
       <c r="B132" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C132" s="29" t="s">
+      <c r="C132" s="20" t="s">
         <v>1340</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -15212,7 +15213,7 @@
       <c r="B133" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C133" s="29" t="s">
+      <c r="C133" s="20" t="s">
         <v>1340</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -15224,7 +15225,7 @@
       <c r="B134" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C134" s="29" t="s">
+      <c r="C134" s="20" t="s">
         <v>1341</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -15236,7 +15237,7 @@
       <c r="B135" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C135" s="29" t="s">
+      <c r="C135" s="20" t="s">
         <v>1341</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -15260,7 +15261,7 @@
       <c r="B137" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C137" s="29" t="s">
+      <c r="C137" s="20" t="s">
         <v>1343</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -15272,7 +15273,7 @@
       <c r="B138" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C138" s="29" t="s">
+      <c r="C138" s="20" t="s">
         <v>1343</v>
       </c>
       <c r="D138" s="1" t="s">
@@ -15284,7 +15285,7 @@
       <c r="B139" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C139" s="29" t="s">
+      <c r="C139" s="20" t="s">
         <v>1343</v>
       </c>
       <c r="D139" s="1" t="s">

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1854BF3-26A9-4B08-B73E-9BFDC3979107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5E393B-EE46-468E-B30B-AC200CFE9BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50730" yWindow="2085" windowWidth="28770" windowHeight="15450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51900" yWindow="2055" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="1391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="1397">
   <si>
     <t>food</t>
   </si>
@@ -5197,6 +5197,28 @@
   </si>
   <si>
     <t>아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 북구 연경중앙로 55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 북구 도남길 148-51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 북구 구리로 254</t>
+  </si>
+  <si>
+    <t>대구광역시 북구 국우동 1079</t>
+  </si>
+  <si>
+    <t>대구 북구 국우동 1079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 북구 읍내동 794</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11535,7 +11557,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1EB988-2ED1-436F-8BF0-F3686DC619B0}">
-  <dimension ref="A1:T166"/>
+  <dimension ref="A1:T172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -11817,68 +11839,68 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>1353</v>
+        <v>1267</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1354</v>
+        <v>1277</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>1353</v>
+        <v>1267</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1354</v>
+        <v>1278</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>1353</v>
+        <v>1267</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1354</v>
+        <v>1279</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1335</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>1353</v>
+        <v>1267</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1355</v>
+        <v>1277</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>1353</v>
+        <v>1267</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1355</v>
+        <v>1278</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>1353</v>
+        <v>1267</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1355</v>
+        <v>1279</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11886,10 +11908,10 @@
         <v>1353</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11897,10 +11919,10 @@
         <v>1353</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1342</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -11908,51 +11930,51 @@
         <v>1353</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1332</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>1351</v>
@@ -11960,10 +11982,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>1342</v>
@@ -11971,10 +11993,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>1346</v>
@@ -11985,7 +12007,7 @@
         <v>1357</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>1351</v>
@@ -11996,10 +12018,10 @@
         <v>1357</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -12007,18 +12029,18 @@
         <v>1357</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1346</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1368</v>
+        <v>1359</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>1351</v>
@@ -12026,57 +12048,57 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1368</v>
+        <v>1359</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1368</v>
+        <v>1359</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1335</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1369</v>
+        <v>1360</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1369</v>
+        <v>1360</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1369</v>
+        <v>1360</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1370</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -12084,7 +12106,7 @@
         <v>1367</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>1351</v>
@@ -12095,10 +12117,10 @@
         <v>1367</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -12106,51 +12128,51 @@
         <v>1367</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1374</v>
+        <v>1391</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1374</v>
+        <v>1391</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1374</v>
+        <v>1391</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1346</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>1351</v>
@@ -12158,10 +12180,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>1342</v>
@@ -12169,10 +12191,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>1346</v>
@@ -12183,7 +12205,7 @@
         <v>1373</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>1351</v>
@@ -12194,7 +12216,7 @@
         <v>1373</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>1342</v>
@@ -12205,7 +12227,7 @@
         <v>1373</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>1346</v>
@@ -12213,10 +12235,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>1351</v>
@@ -12224,10 +12246,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>1342</v>
@@ -12235,10 +12257,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>1346</v>
@@ -12246,35 +12268,35 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -12282,7 +12304,7 @@
         <v>1377</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>1351</v>
@@ -12293,10 +12315,10 @@
         <v>1377</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -12304,76 +12326,76 @@
         <v>1377</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1335</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1" t="s">
-        <v>1272</v>
+        <v>1377</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1288</v>
+        <v>1393</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>1272</v>
+        <v>1377</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1288</v>
+        <v>1393</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>1272</v>
+        <v>1377</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1288</v>
+        <v>1393</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>1272</v>
+        <v>1377</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>1272</v>
+        <v>1377</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>1272</v>
+        <v>1377</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1350</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -12381,10 +12403,10 @@
         <v>1272</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -12392,10 +12414,10 @@
         <v>1272</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -12403,51 +12425,51 @@
         <v>1272</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>1382</v>
+        <v>1272</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1354</v>
+        <v>1381</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>1382</v>
+        <v>1272</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1354</v>
+        <v>1381</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1331</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>1382</v>
+        <v>1272</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1354</v>
+        <v>1381</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1335</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
-        <v>1382</v>
+        <v>1272</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1355</v>
+        <v>1287</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>1348</v>
@@ -12455,24 +12477,24 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
-        <v>1382</v>
+        <v>1272</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1355</v>
+        <v>1287</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="1" t="s">
-        <v>1382</v>
+        <v>1272</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1355</v>
+        <v>1287</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>1350</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -12480,10 +12502,10 @@
         <v>1382</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -12491,10 +12513,10 @@
         <v>1382</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1342</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -12502,51 +12524,51 @@
         <v>1382</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>1351</v>
@@ -12554,24 +12576,24 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1335</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -12579,7 +12601,7 @@
         <v>1383</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>1351</v>
@@ -12590,7 +12612,7 @@
         <v>1383</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>1342</v>
@@ -12601,7 +12623,7 @@
         <v>1383</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1346</v>
@@ -12609,10 +12631,10 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>1273</v>
+        <v>1383</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1384</v>
+        <v>1359</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>1351</v>
@@ -12620,57 +12642,57 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1" t="s">
-        <v>1273</v>
+        <v>1383</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1384</v>
+        <v>1359</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
-        <v>1273</v>
+        <v>1383</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1384</v>
+        <v>1359</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
-        <v>1273</v>
+        <v>1383</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1287</v>
+        <v>1358</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>1273</v>
+        <v>1383</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1287</v>
+        <v>1358</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>1273</v>
+        <v>1383</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1287</v>
+        <v>1358</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -12678,7 +12700,7 @@
         <v>1273</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1289</v>
+        <v>1395</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>1351</v>
@@ -12689,7 +12711,7 @@
         <v>1273</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>1289</v>
+        <v>1395</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>1342</v>
@@ -12700,7 +12722,7 @@
         <v>1273</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1289</v>
+        <v>1395</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>1346</v>
@@ -12708,68 +12730,68 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="1" t="s">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1386</v>
+        <v>1287</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="1" t="s">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1386</v>
+        <v>1287</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="1" t="s">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1386</v>
+        <v>1287</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="1" t="s">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1362</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="1" t="s">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1363</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1364</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -12777,10 +12799,10 @@
         <v>1385</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1287</v>
+        <v>1396</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -12788,10 +12810,10 @@
         <v>1385</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1287</v>
+        <v>1396</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -12799,76 +12821,76 @@
         <v>1385</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1287</v>
+        <v>1396</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>1351</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1342</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1346</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>1384</v>
+        <v>1287</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1384</v>
+        <v>1287</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1384</v>
+        <v>1287</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>1346</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -12876,7 +12898,7 @@
         <v>1387</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1360</v>
+        <v>1288</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>1351</v>
@@ -12887,7 +12909,7 @@
         <v>1387</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1360</v>
+        <v>1288</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>1342</v>
@@ -12898,85 +12920,341 @@
         <v>1387</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>1360</v>
+        <v>1288</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>1346</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
+      <c r="A122" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>1351</v>
+      </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
+      <c r="A123" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>1342</v>
+      </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
+      <c r="A124" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>1346</v>
+      </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
+      <c r="A125" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>1351</v>
+      </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
+      <c r="A126" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>1342</v>
+      </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
+      <c r="A127" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>1346</v>
+      </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
     </row>
-    <row r="129" s="2" customFormat="1"/>
-    <row r="130" s="2" customFormat="1"/>
-    <row r="131" s="2" customFormat="1"/>
-    <row r="132" s="2" customFormat="1"/>
-    <row r="133" s="2" customFormat="1"/>
-    <row r="134" s="2" customFormat="1"/>
-    <row r="135" s="2" customFormat="1"/>
-    <row r="136" s="2" customFormat="1"/>
-    <row r="137" s="2" customFormat="1"/>
-    <row r="138" s="2" customFormat="1"/>
-    <row r="139" s="2" customFormat="1"/>
-    <row r="140" s="2" customFormat="1"/>
-    <row r="141" s="2" customFormat="1"/>
-    <row r="142" s="2" customFormat="1"/>
-    <row r="143" s="2" customFormat="1"/>
-    <row r="144" s="2" customFormat="1"/>
-    <row r="145" s="2" customFormat="1"/>
-    <row r="146" s="2" customFormat="1"/>
-    <row r="147" s="2" customFormat="1"/>
-    <row r="148" s="2" customFormat="1"/>
-    <row r="149" s="2" customFormat="1"/>
-    <row r="150" s="2" customFormat="1"/>
-    <row r="151" s="2" customFormat="1"/>
-    <row r="152" s="2" customFormat="1"/>
-    <row r="153" s="2" customFormat="1"/>
-    <row r="154" s="2" customFormat="1"/>
-    <row r="155" s="2" customFormat="1"/>
-    <row r="156" s="2" customFormat="1"/>
-    <row r="157" s="2" customFormat="1"/>
-    <row r="158" s="2" customFormat="1"/>
-    <row r="159" s="2" customFormat="1"/>
-    <row r="160" s="2" customFormat="1"/>
-    <row r="161" s="2" customFormat="1"/>
-    <row r="162" s="2" customFormat="1"/>
-    <row r="163" s="2" customFormat="1"/>
-    <row r="164" s="2" customFormat="1"/>
-    <row r="165" s="2" customFormat="1"/>
-    <row r="166" s="2" customFormat="1"/>
+    <row r="129" spans="1:17">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+    </row>
+    <row r="130" spans="1:17">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+    </row>
+    <row r="131" spans="1:17">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+    </row>
+    <row r="132" spans="1:17">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+    </row>
+    <row r="133" spans="1:17">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+    </row>
+    <row r="134" spans="1:17">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+    </row>
+    <row r="135" spans="1:17">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="Q135" s="2"/>
+    </row>
+    <row r="136" spans="1:17">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="Q136" s="2"/>
+    </row>
+    <row r="137" spans="1:17">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="Q137" s="2"/>
+    </row>
+    <row r="138" spans="1:17">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="Q138" s="2"/>
+    </row>
+    <row r="139" spans="1:17">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="Q139" s="2"/>
+    </row>
+    <row r="140" spans="1:17">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="Q140" s="2"/>
+    </row>
+    <row r="141" spans="1:17">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="Q141" s="2"/>
+    </row>
+    <row r="142" spans="1:17">
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="Q142" s="2"/>
+    </row>
+    <row r="143" spans="1:17">
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="Q143" s="2"/>
+    </row>
+    <row r="144" spans="1:17">
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="Q144" s="2"/>
+    </row>
+    <row r="145" spans="1:17">
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="Q145" s="2"/>
+    </row>
+    <row r="146" spans="1:17">
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="Q146" s="2"/>
+    </row>
+    <row r="147" spans="1:17">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="Q147" s="2"/>
+    </row>
+    <row r="148" spans="1:17">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="Q148" s="2"/>
+    </row>
+    <row r="149" spans="1:17">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="Q149" s="2"/>
+    </row>
+    <row r="150" spans="1:17">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="Q150" s="2"/>
+    </row>
+    <row r="151" spans="1:17">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="Q151" s="2"/>
+    </row>
+    <row r="152" spans="1:17">
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="Q152" s="2"/>
+    </row>
+    <row r="153" spans="1:17">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="Q153" s="2"/>
+    </row>
+    <row r="154" spans="1:17">
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="Q154" s="2"/>
+    </row>
+    <row r="155" spans="1:17">
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="Q155" s="2"/>
+    </row>
+    <row r="156" spans="1:17">
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="Q156" s="2"/>
+    </row>
+    <row r="157" spans="1:17">
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="Q157" s="2"/>
+    </row>
+    <row r="158" spans="1:17">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="Q158" s="2"/>
+    </row>
+    <row r="159" spans="1:17">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="Q159" s="2"/>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="Q160" s="2"/>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="Q161" s="2"/>
+    </row>
+    <row r="162" spans="1:17">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="Q162" s="2"/>
+    </row>
+    <row r="163" spans="1:17">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="Q163" s="2"/>
+    </row>
+    <row r="164" spans="1:17">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="Q164" s="2"/>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="Q165" s="2"/>
+    </row>
+    <row r="166" spans="1:17">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="Q166" s="2"/>
+    </row>
+    <row r="167" spans="1:17">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="Q167" s="2"/>
+    </row>
+    <row r="168" spans="1:17">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="Q168" s="2"/>
+    </row>
+    <row r="169" spans="1:17">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="Q169" s="2"/>
+    </row>
+    <row r="170" spans="1:17">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="Q170" s="2"/>
+    </row>
+    <row r="171" spans="1:17">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="Q171" s="2"/>
+    </row>
+    <row r="172" spans="1:17">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="Q172" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5E393B-EE46-468E-B30B-AC200CFE9BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC453E88-1CDE-40A2-B8FD-37A0F7586A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51900" yWindow="2055" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -5900,25 +5900,25 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:X501"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="17.25" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="48.625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.19921875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="48.59765625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" style="2"/>
-    <col min="11" max="12" width="10.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.75"/>
+    <col min="11" max="12" width="10.59765625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.69921875"/>
     <col min="14" max="14" width="9" style="2"/>
-    <col min="15" max="16" width="10.625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.75"/>
+    <col min="15" max="16" width="10.59765625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="8.69921875"/>
     <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="20.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -5952,7 +5952,7 @@
         <v>1263</v>
       </c>
       <c r="T1" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="V1"/>
       <c r="W1"/>
@@ -6025,7 +6025,7 @@
         <v>1265</v>
       </c>
       <c r="T3" s="2">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>
@@ -6451,7 +6451,7 @@
       <c r="T17" s="25"/>
       <c r="U17" s="26"/>
     </row>
-    <row r="18" spans="1:21" ht="17.25">
+    <row r="18" spans="1:21" ht="19.2">
       <c r="A18" s="2"/>
       <c r="B18" s="15"/>
       <c r="C18" s="2"/>
@@ -6559,7 +6559,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="17.25">
+    <row r="22" spans="1:21" ht="19.2">
       <c r="A22" s="2"/>
       <c r="B22" s="16"/>
       <c r="C22" s="2"/>
@@ -11557,18 +11557,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1EB988-2ED1-436F-8BF0-F3686DC619B0}">
-  <dimension ref="A1:T172"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:T127"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
     <col min="5" max="16" width="9" style="2" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -12991,269 +12991,6 @@
       <c r="C127" s="1" t="s">
         <v>1346</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-    </row>
-    <row r="129" spans="1:17">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-    </row>
-    <row r="130" spans="1:17">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-    </row>
-    <row r="131" spans="1:17">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-    </row>
-    <row r="132" spans="1:17">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-    </row>
-    <row r="133" spans="1:17">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-    </row>
-    <row r="134" spans="1:17">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
-    </row>
-    <row r="135" spans="1:17">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="Q135" s="2"/>
-    </row>
-    <row r="136" spans="1:17">
-      <c r="A136" s="2"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="Q136" s="2"/>
-    </row>
-    <row r="137" spans="1:17">
-      <c r="A137" s="2"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="Q137" s="2"/>
-    </row>
-    <row r="138" spans="1:17">
-      <c r="A138" s="2"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
-      <c r="Q138" s="2"/>
-    </row>
-    <row r="139" spans="1:17">
-      <c r="A139" s="2"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
-      <c r="Q139" s="2"/>
-    </row>
-    <row r="140" spans="1:17">
-      <c r="A140" s="2"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="Q140" s="2"/>
-    </row>
-    <row r="141" spans="1:17">
-      <c r="A141" s="2"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="Q141" s="2"/>
-    </row>
-    <row r="142" spans="1:17">
-      <c r="A142" s="2"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="Q142" s="2"/>
-    </row>
-    <row r="143" spans="1:17">
-      <c r="A143" s="2"/>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="Q143" s="2"/>
-    </row>
-    <row r="144" spans="1:17">
-      <c r="A144" s="2"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="Q144" s="2"/>
-    </row>
-    <row r="145" spans="1:17">
-      <c r="A145" s="2"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="Q145" s="2"/>
-    </row>
-    <row r="146" spans="1:17">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="Q146" s="2"/>
-    </row>
-    <row r="147" spans="1:17">
-      <c r="A147" s="2"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="Q147" s="2"/>
-    </row>
-    <row r="148" spans="1:17">
-      <c r="A148" s="2"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="Q148" s="2"/>
-    </row>
-    <row r="149" spans="1:17">
-      <c r="A149" s="2"/>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="Q149" s="2"/>
-    </row>
-    <row r="150" spans="1:17">
-      <c r="A150" s="2"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
-      <c r="Q150" s="2"/>
-    </row>
-    <row r="151" spans="1:17">
-      <c r="A151" s="2"/>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
-      <c r="Q151" s="2"/>
-    </row>
-    <row r="152" spans="1:17">
-      <c r="A152" s="2"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
-      <c r="Q152" s="2"/>
-    </row>
-    <row r="153" spans="1:17">
-      <c r="A153" s="2"/>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
-      <c r="Q153" s="2"/>
-    </row>
-    <row r="154" spans="1:17">
-      <c r="A154" s="2"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
-      <c r="Q154" s="2"/>
-    </row>
-    <row r="155" spans="1:17">
-      <c r="A155" s="2"/>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
-      <c r="Q155" s="2"/>
-    </row>
-    <row r="156" spans="1:17">
-      <c r="A156" s="2"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
-      <c r="Q156" s="2"/>
-    </row>
-    <row r="157" spans="1:17">
-      <c r="A157" s="2"/>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
-      <c r="Q157" s="2"/>
-    </row>
-    <row r="158" spans="1:17">
-      <c r="A158" s="2"/>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
-      <c r="Q158" s="2"/>
-    </row>
-    <row r="159" spans="1:17">
-      <c r="A159" s="2"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="Q159" s="2"/>
-    </row>
-    <row r="160" spans="1:17">
-      <c r="A160" s="2"/>
-      <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
-      <c r="Q160" s="2"/>
-    </row>
-    <row r="161" spans="1:17">
-      <c r="A161" s="2"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
-      <c r="Q161" s="2"/>
-    </row>
-    <row r="162" spans="1:17">
-      <c r="A162" s="2"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
-      <c r="Q162" s="2"/>
-    </row>
-    <row r="163" spans="1:17">
-      <c r="A163" s="2"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
-      <c r="Q163" s="2"/>
-    </row>
-    <row r="164" spans="1:17">
-      <c r="A164" s="2"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="Q164" s="2"/>
-    </row>
-    <row r="165" spans="1:17">
-      <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
-      <c r="Q165" s="2"/>
-    </row>
-    <row r="166" spans="1:17">
-      <c r="A166" s="2"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
-      <c r="Q166" s="2"/>
-    </row>
-    <row r="167" spans="1:17">
-      <c r="A167" s="2"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
-      <c r="Q167" s="2"/>
-    </row>
-    <row r="168" spans="1:17">
-      <c r="A168" s="2"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
-      <c r="Q168" s="2"/>
-    </row>
-    <row r="169" spans="1:17">
-      <c r="A169" s="2"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
-      <c r="Q169" s="2"/>
-    </row>
-    <row r="170" spans="1:17">
-      <c r="A170" s="2"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
-      <c r="Q170" s="2"/>
-    </row>
-    <row r="171" spans="1:17">
-      <c r="A171" s="2"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
-      <c r="Q171" s="2"/>
-    </row>
-    <row r="172" spans="1:17">
-      <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="Q172" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13269,14 +13006,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801651D1-1060-4046-8C27-A9334BE84870}">
   <dimension ref="A1:T63"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -13357,7 +13094,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.25">
+    <row r="7" spans="1:20" ht="19.2">
       <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
@@ -13401,7 +13138,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.25">
+    <row r="11" spans="1:20" ht="19.2">
       <c r="A11" s="7" t="s">
         <v>5</v>
       </c>
@@ -13423,7 +13160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.25">
+    <row r="13" spans="1:20" ht="19.2">
       <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
@@ -13698,7 +13435,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="17.25">
+    <row r="38" spans="1:3" ht="19.2">
       <c r="A38" s="7" t="s">
         <v>1298</v>
       </c>
@@ -13742,7 +13479,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="17.25">
+    <row r="42" spans="1:3" ht="19.2">
       <c r="A42" s="7" t="s">
         <v>1299</v>
       </c>
@@ -13895,9 +13632,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECF04CD-0782-4755-8611-A09CA217F0DE}">
   <dimension ref="A1:D166"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15522,7 +15259,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25">
+    <row r="136" spans="1:4" ht="19.2">
       <c r="A136" s="30"/>
       <c r="B136" s="1" t="s">
         <v>1271</v>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC453E88-1CDE-40A2-B8FD-37A0F7586A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51277F19-846A-4BB2-9F30-C1644E809226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5952,7 +5952,7 @@
         <v>1263</v>
       </c>
       <c r="T1" s="2">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="V1"/>
       <c r="W1"/>
@@ -5988,7 +5988,7 @@
         <v>1264</v>
       </c>
       <c r="T2" s="2">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
@@ -6025,7 +6025,7 @@
         <v>1265</v>
       </c>
       <c r="T3" s="2">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51277F19-846A-4BB2-9F30-C1644E809226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E608C3-F63A-42BD-A48D-1844E8B8E54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5988,7 +5988,7 @@
         <v>1264</v>
       </c>
       <c r="T2" s="2">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
@@ -6025,7 +6025,7 @@
         <v>1265</v>
       </c>
       <c r="T3" s="2">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E608C3-F63A-42BD-A48D-1844E8B8E54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142734ED-8151-4AE3-928F-ED2CCD97A710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2472" yWindow="732" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -5988,7 +5988,7 @@
         <v>1264</v>
       </c>
       <c r="T2" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
@@ -6025,7 +6025,7 @@
         <v>1265</v>
       </c>
       <c r="T3" s="2">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142734ED-8151-4AE3-928F-ED2CCD97A710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896CD826-8A2E-4F0C-AD93-ED443ECA9B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2472" yWindow="732" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5952,7 +5952,7 @@
         <v>1263</v>
       </c>
       <c r="T1" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="V1"/>
       <c r="W1"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896CD826-8A2E-4F0C-AD93-ED443ECA9B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB1784D-BAE7-438A-84FB-712507AA5B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="732" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="564" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -5952,7 +5952,7 @@
         <v>1263</v>
       </c>
       <c r="T1" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="V1"/>
       <c r="W1"/>
@@ -5988,7 +5988,7 @@
         <v>1264</v>
       </c>
       <c r="T2" s="2">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
@@ -6025,7 +6025,7 @@
         <v>1265</v>
       </c>
       <c r="T3" s="2">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>
